--- a/exports/trend_1d/BLUESTARCO_full_report.xlsx
+++ b/exports/trend_1d/BLUESTARCO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q66"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>10.04</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42041</v>
+        <v>42044</v>
       </c>
       <c r="H2" t="n">
-        <v>167.5</v>
+        <v>157.15</v>
       </c>
       <c r="I2" t="n">
         <v>164.9028275</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.64</v>
+        <v>-7.72</v>
       </c>
       <c r="L2" t="n">
-        <v>6.34</v>
+        <v>8.4</v>
       </c>
       <c r="M2" t="n">
         <v>1.61</v>
       </c>
       <c r="N2" t="n">
-        <v>3.84</v>
+        <v>6.18</v>
       </c>
       <c r="O2" t="n">
         <v>4.77</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>16.51</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42143</v>
+        <v>42144</v>
       </c>
       <c r="H3" t="n">
-        <v>166.55</v>
+        <v>170</v>
       </c>
       <c r="I3" t="n">
         <v>167.7845652255949</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.98</v>
+        <v>-8.18</v>
       </c>
       <c r="L3" t="n">
         <v>8.81</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.07</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42268</v>
+        <v>42269</v>
       </c>
       <c r="H4" t="n">
-        <v>169</v>
+        <v>166.7</v>
       </c>
       <c r="I4" t="n">
         <v>167.6235564629077</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.59</v>
+        <v>-1.94</v>
       </c>
       <c r="L4" t="n">
         <v>7.29</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.23</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42290</v>
+        <v>42291</v>
       </c>
       <c r="H5" t="n">
-        <v>178.1</v>
+        <v>180.4</v>
       </c>
       <c r="I5" t="n">
         <v>178.5402191809594</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.84</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>7.98</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M5" t="n">
         <v>1.86</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>12.38</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H6" t="n">
-        <v>181.1</v>
+        <v>169</v>
       </c>
       <c r="I6" t="n">
         <v>176.3116764155416</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" t="n">
-        <v>0.39</v>
+        <v>-6.32</v>
       </c>
       <c r="L6" t="n">
         <v>8.199999999999999</v>
@@ -783,7 +854,7 @@
         <v>7.25</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>6.68</v>
       </c>
       <c r="O6" t="n">
         <v>1.29</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>15.48</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42444</v>
+        <v>42445</v>
       </c>
       <c r="H7" t="n">
-        <v>173.1</v>
+        <v>178.8</v>
       </c>
       <c r="I7" t="n">
         <v>178.3168875517863</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.43</v>
+        <v>-5.8</v>
       </c>
       <c r="L7" t="n">
         <v>9.140000000000001</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>12.66</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42684</v>
+        <v>42685</v>
       </c>
       <c r="H8" t="n">
-        <v>264.9</v>
+        <v>254.95</v>
       </c>
       <c r="I8" t="n">
         <v>263.2874376540454</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K8" t="n">
-        <v>48.15</v>
+        <v>42.59</v>
       </c>
       <c r="L8" t="n">
         <v>2.96</v>
@@ -897,7 +992,7 @@
         <v>19.97</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.76</v>
       </c>
       <c r="O8" t="n">
         <v>3.29</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>160</v>
+        <v>161</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>17.78</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42738</v>
+        <v>42739</v>
       </c>
       <c r="H9" t="n">
-        <v>244.95</v>
+        <v>245.1</v>
       </c>
       <c r="I9" t="n">
         <v>244.964598488089</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K9" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="L9" t="n">
         <v>4.92</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42873</v>
+        <v>42874</v>
       </c>
       <c r="H10" t="n">
-        <v>324.7</v>
+        <v>323.3</v>
       </c>
       <c r="I10" t="n">
         <v>324.1982320838433</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K10" t="n">
-        <v>32.48</v>
+        <v>31.91</v>
       </c>
       <c r="L10" t="n">
         <v>1.26</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>11.61</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42934</v>
+        <v>42935</v>
       </c>
       <c r="H11" t="n">
-        <v>327.9</v>
+        <v>331.85</v>
       </c>
       <c r="I11" t="n">
         <v>327.9110123364104</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.42</v>
+        <v>-2.64</v>
       </c>
       <c r="L11" t="n">
         <v>5.17</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>11.07</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43040</v>
+        <v>43041</v>
       </c>
       <c r="H12" t="n">
-        <v>383</v>
+        <v>359.85</v>
       </c>
       <c r="I12" t="n">
         <v>364.9624579025609</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K12" t="n">
-        <v>15.41</v>
+        <v>8.44</v>
       </c>
       <c r="L12" t="n">
         <v>6.58</v>
@@ -1125,7 +1268,7 @@
         <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.6</v>
+        <v>6.04</v>
       </c>
       <c r="O12" t="n">
         <v>1.2</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>16.67</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43074</v>
+        <v>43075</v>
       </c>
       <c r="H13" t="n">
-        <v>375.4</v>
+        <v>382.3</v>
       </c>
       <c r="I13" t="n">
         <v>377.7940449469174</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.32</v>
+        <v>-6.24</v>
       </c>
       <c r="L13" t="n">
         <v>7.27</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>12.6</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43116</v>
+        <v>43117</v>
       </c>
       <c r="H14" t="n">
-        <v>379.2</v>
+        <v>371.7</v>
       </c>
       <c r="I14" t="n">
         <v>376.6256238272783</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-2.77</v>
       </c>
       <c r="L14" t="n">
-        <v>2.96</v>
+        <v>3.87</v>
       </c>
       <c r="M14" t="n">
         <v>2.47</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.98</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43173</v>
+        <v>43174</v>
       </c>
       <c r="H15" t="n">
-        <v>400.5</v>
+        <v>401.6</v>
       </c>
       <c r="I15" t="n">
         <v>401.5495657543121</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.75</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>10.28</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43237</v>
+        <v>43238</v>
       </c>
       <c r="H16" t="n">
-        <v>381.5</v>
+        <v>368.5</v>
       </c>
       <c r="I16" t="n">
         <v>370.3660274345459</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K16" t="n">
-        <v>-5</v>
+        <v>-8.24</v>
       </c>
       <c r="L16" t="n">
-        <v>8.24</v>
+        <v>8.91</v>
       </c>
       <c r="M16" t="n">
         <v>0.57</v>
       </c>
       <c r="N16" t="n">
-        <v>2.47</v>
+        <v>3.41</v>
       </c>
       <c r="O16" t="n">
         <v>0.27</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>11.35</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43320</v>
+        <v>43321</v>
       </c>
       <c r="H17" t="n">
-        <v>344.8</v>
+        <v>349.6</v>
       </c>
       <c r="I17" t="n">
         <v>348.6034141383648</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K17" t="n">
-        <v>6.43</v>
+        <v>5.13</v>
       </c>
       <c r="L17" t="n">
         <v>3.53</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>9.08</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43364</v>
+        <v>43367</v>
       </c>
       <c r="H18" t="n">
-        <v>325.3</v>
+        <v>312.8</v>
       </c>
       <c r="I18" t="n">
         <v>318.3304281780818</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.95</v>
+        <v>-10.53</v>
       </c>
       <c r="L18" t="n">
-        <v>8.970000000000001</v>
+        <v>12.39</v>
       </c>
       <c r="M18" t="n">
-        <v>0.48</v>
+        <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="O18" t="n">
         <v>1.39</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>10.12</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43418</v>
+        <v>43419</v>
       </c>
       <c r="H19" t="n">
-        <v>288.2</v>
+        <v>295.8</v>
       </c>
       <c r="I19" t="n">
         <v>292.5455988576621</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K19" t="n">
-        <v>7.86</v>
+        <v>5.43</v>
       </c>
       <c r="L19" t="n">
         <v>3.13</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.68</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43493</v>
+        <v>43494</v>
       </c>
       <c r="H20" t="n">
-        <v>302.6</v>
+        <v>300.8</v>
       </c>
       <c r="I20" t="n">
         <v>302.3015102624555</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="L20" t="n">
         <v>2.81</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.21</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43523</v>
+        <v>43524</v>
       </c>
       <c r="H21" t="n">
-        <v>304.9</v>
+        <v>310.4</v>
       </c>
       <c r="I21" t="n">
         <v>308.2835411940188</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.36</v>
+        <v>-3.19</v>
       </c>
       <c r="L21" t="n">
         <v>4.06</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>10.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43573</v>
+        <v>43577</v>
       </c>
       <c r="H22" t="n">
-        <v>329.45</v>
+        <v>325.8</v>
       </c>
       <c r="I22" t="n">
         <v>326.9993579445667</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K22" t="n">
-        <v>6.14</v>
+        <v>4.96</v>
       </c>
       <c r="L22" t="n">
         <v>2.55</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>7.68</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43588</v>
+        <v>43591</v>
       </c>
       <c r="H23" t="n">
-        <v>349.2</v>
+        <v>355.5</v>
       </c>
       <c r="I23" t="n">
         <v>350.830867366053</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.18</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>8.9</v>
+        <v>9.56</v>
       </c>
       <c r="M23" t="n">
         <v>2.11</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>11.21</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H24" t="n">
-        <v>376.8</v>
+        <v>366.9</v>
       </c>
       <c r="I24" t="n">
         <v>367.4203529044298</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K24" t="n">
-        <v>5.99</v>
+        <v>3.21</v>
       </c>
       <c r="L24" t="n">
         <v>4.08</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>11.37</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43684</v>
+        <v>43685</v>
       </c>
       <c r="H25" t="n">
-        <v>349.35</v>
+        <v>370.2</v>
       </c>
       <c r="I25" t="n">
         <v>368.3149257910571</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>4.78</v>
+        <v>-0.9</v>
       </c>
       <c r="L25" t="n">
         <v>4.12</v>
@@ -1866,7 +2165,7 @@
         <v>1.52</v>
       </c>
       <c r="N25" t="n">
-        <v>5.71</v>
+        <v>5.97</v>
       </c>
       <c r="O25" t="n">
         <v>-2.63</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>15.6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43795</v>
+        <v>43796</v>
       </c>
       <c r="H26" t="n">
-        <v>396.3</v>
+        <v>390.95</v>
       </c>
       <c r="I26" t="n">
         <v>391.98299589048</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K26" t="n">
-        <v>7.05</v>
+        <v>5.61</v>
       </c>
       <c r="L26" t="n">
         <v>7.46</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.21</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43829</v>
+        <v>43830</v>
       </c>
       <c r="H27" t="n">
-        <v>402.9</v>
+        <v>420.4</v>
       </c>
       <c r="I27" t="n">
         <v>419.8941048363413</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>-3.06</v>
+        <v>-7.53</v>
       </c>
       <c r="L27" t="n">
-        <v>4.82</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M27" t="n">
         <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>1.44</v>
+        <v>4.34</v>
       </c>
       <c r="O27" t="n">
         <v>-1.35</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43871</v>
+        <v>43872</v>
       </c>
       <c r="H28" t="n">
-        <v>400.3</v>
+        <v>398.2</v>
       </c>
       <c r="I28" t="n">
         <v>399.8046330522481</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.78</v>
+        <v>-5.28</v>
       </c>
       <c r="L28" t="n">
-        <v>5.52</v>
+        <v>5.99</v>
       </c>
       <c r="M28" t="n">
         <v>1.27</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.59</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H29" t="n">
-        <v>258.1</v>
+        <v>269.3</v>
       </c>
       <c r="I29" t="n">
         <v>262.6481172122407</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K29" t="n">
-        <v>35.18</v>
+        <v>32.37</v>
       </c>
       <c r="L29" t="n">
         <v>8.48</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>5</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>14.97</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44025</v>
+        <v>44026</v>
       </c>
       <c r="H30" t="n">
-        <v>240.1</v>
+        <v>234.3</v>
       </c>
       <c r="I30" t="n">
         <v>235.6006621990487</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K30" t="n">
-        <v>-10.84</v>
+        <v>-13</v>
       </c>
       <c r="L30" t="n">
-        <v>11.07</v>
+        <v>13.67</v>
       </c>
       <c r="M30" t="n">
         <v>2.79</v>
       </c>
       <c r="N30" t="n">
-        <v>2.29</v>
+        <v>2.42</v>
       </c>
       <c r="O30" t="n">
         <v>4.34</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44050</v>
+        <v>44053</v>
       </c>
       <c r="H31" t="n">
-        <v>249.1</v>
+        <v>257.2</v>
       </c>
       <c r="I31" t="n">
         <v>256.3090054399444</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.32</v>
+        <v>-9.77</v>
       </c>
       <c r="L31" t="n">
-        <v>9.050000000000001</v>
+        <v>11.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.1</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44042</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.57</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H32" t="n">
-        <v>374.1</v>
+        <v>368</v>
       </c>
       <c r="I32" t="n">
         <v>370.5542940808311</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K32" t="n">
-        <v>45.45</v>
+        <v>43.08</v>
       </c>
       <c r="L32" t="n">
         <v>2.8</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>6</v>
+      </c>
+      <c r="U32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>12.65</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44231</v>
+        <v>44232</v>
       </c>
       <c r="H33" t="n">
-        <v>401</v>
+        <v>407.5</v>
       </c>
       <c r="I33" t="n">
         <v>404.726518707059</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K33" t="n">
-        <v>-8.970000000000001</v>
+        <v>-10.73</v>
       </c>
       <c r="L33" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="M33" t="n">
         <v>0.98</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>11.26</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44302</v>
+        <v>44305</v>
       </c>
       <c r="H34" t="n">
-        <v>428.8</v>
+        <v>413.6</v>
       </c>
       <c r="I34" t="n">
         <v>418.5403667291483</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K34" t="n">
-        <v>5.23</v>
+        <v>1.5</v>
       </c>
       <c r="L34" t="n">
         <v>3.29</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.31</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44379</v>
+        <v>44382</v>
       </c>
       <c r="H35" t="n">
-        <v>415.2</v>
+        <v>436.3</v>
       </c>
       <c r="I35" t="n">
         <v>430.8286168336631</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.39</v>
+        <v>-5.49</v>
       </c>
       <c r="L35" t="n">
         <v>6.99</v>
@@ -2436,7 +2855,7 @@
         <v>3.28</v>
       </c>
       <c r="N35" t="n">
-        <v>3.4</v>
+        <v>5.08</v>
       </c>
       <c r="O35" t="n">
         <v>-3.54</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>9.5</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44428</v>
+        <v>44431</v>
       </c>
       <c r="H36" t="n">
-        <v>405.9</v>
+        <v>400.1</v>
       </c>
       <c r="I36" t="n">
         <v>400.7120225460253</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K36" t="n">
-        <v>-6.97</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>9.4</v>
+        <v>10.61</v>
       </c>
       <c r="M36" t="n">
         <v>1.42</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44448</v>
+        <v>44452</v>
       </c>
       <c r="H37" t="n">
-        <v>416.2</v>
+        <v>423.05</v>
       </c>
       <c r="I37" t="n">
         <v>421.6439894116144</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.02</v>
+        <v>-5.74</v>
       </c>
       <c r="L37" t="n">
-        <v>6.22</v>
+        <v>6.47</v>
       </c>
       <c r="M37" t="n">
         <v>5.34</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.32</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H38" t="n">
-        <v>492.7</v>
+        <v>468.8</v>
       </c>
       <c r="I38" t="n">
         <v>474.4945985335419</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K38" t="n">
-        <v>16.46</v>
+        <v>10.81</v>
       </c>
       <c r="L38" t="n">
         <v>3.45</v>
@@ -2607,7 +3062,7 @@
         <v>0.64</v>
       </c>
       <c r="N38" t="n">
-        <v>2.93</v>
+        <v>4.85</v>
       </c>
       <c r="O38" t="n">
         <v>1.65</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>16.15</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44594</v>
+        <v>44595</v>
       </c>
       <c r="H39" t="n">
-        <v>456</v>
+        <v>500</v>
       </c>
       <c r="I39" t="n">
         <v>486.3164419504496</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K39" t="n">
-        <v>2.73</v>
+        <v>-6.66</v>
       </c>
       <c r="L39" t="n">
         <v>14.44</v>
       </c>
       <c r="M39" t="n">
-        <v>1.03</v>
+        <v>2.63</v>
       </c>
       <c r="N39" t="n">
-        <v>4.79</v>
+        <v>9.65</v>
       </c>
       <c r="O39" t="n">
         <v>-4.85</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>16.58</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H40" t="n">
-        <v>545.95</v>
+        <v>536</v>
       </c>
       <c r="I40" t="n">
         <v>536.1053611553589</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K40" t="n">
-        <v>9.19</v>
+        <v>7.2</v>
       </c>
       <c r="L40" t="n">
         <v>7.62</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>17.12</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44755</v>
+        <v>44756</v>
       </c>
       <c r="H41" t="n">
-        <v>471.7</v>
+        <v>487.7</v>
       </c>
       <c r="I41" t="n">
         <v>482.9362997704494</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K41" t="n">
-        <v>12</v>
+        <v>9.01</v>
       </c>
       <c r="L41" t="n">
         <v>8.789999999999999</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>12.93</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45012</v>
+        <v>45013</v>
       </c>
       <c r="H42" t="n">
-        <v>702.9</v>
+        <v>691.6</v>
       </c>
       <c r="I42" t="n">
         <v>699.5729455437239</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K42" t="n">
-        <v>44.13</v>
+        <v>41.81</v>
       </c>
       <c r="L42" t="n">
         <v>4.08</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>175</v>
+        <v>176</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>9</v>
+      </c>
+      <c r="U42" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.09</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45089</v>
+        <v>45090</v>
       </c>
       <c r="H43" t="n">
-        <v>744.4</v>
+        <v>759.2</v>
       </c>
       <c r="I43" t="n">
         <v>756.0140082195566</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K43" t="n">
-        <v>-7.63</v>
+        <v>-9.77</v>
       </c>
       <c r="L43" t="n">
         <v>12.06</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>4</v>
+      </c>
+      <c r="U43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>7.25</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45142</v>
+        <v>45145</v>
       </c>
       <c r="H44" t="n">
-        <v>762.45</v>
+        <v>735.8</v>
       </c>
       <c r="I44" t="n">
         <v>741.0788147863352</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K44" t="n">
-        <v>0.43</v>
+        <v>-3.08</v>
       </c>
       <c r="L44" t="n">
-        <v>2.13</v>
+        <v>5.43</v>
       </c>
       <c r="M44" t="n">
         <v>0.99</v>
       </c>
       <c r="N44" t="n">
-        <v>1.57</v>
+        <v>3.5</v>
       </c>
       <c r="O44" t="n">
         <v>1.99</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45175</v>
+        <v>45176</v>
       </c>
       <c r="H45" t="n">
-        <v>751.25</v>
+        <v>793.05</v>
       </c>
       <c r="I45" t="n">
         <v>765.9237536213193</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.1</v>
+        <v>-7.78</v>
       </c>
       <c r="L45" t="n">
-        <v>4.15</v>
+        <v>8.73</v>
       </c>
       <c r="M45" t="n">
         <v>0.82</v>
       </c>
       <c r="N45" t="n">
-        <v>3.16</v>
+        <v>5.56</v>
       </c>
       <c r="O45" t="n">
         <v>-3.5</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.25</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45587</v>
+        <v>45588</v>
       </c>
       <c r="H46" t="n">
-        <v>1910.05</v>
+        <v>1900.15</v>
       </c>
       <c r="I46" t="n">
         <v>1904.24530181452</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K46" t="n">
-        <v>140.85</v>
+        <v>139.6</v>
       </c>
       <c r="L46" t="n">
         <v>5.43</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>279</v>
+        <v>280</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>14</v>
+      </c>
+      <c r="U46" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>13.03</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45631</v>
+        <v>45632</v>
       </c>
       <c r="H47" t="n">
-        <v>1965.95</v>
+        <v>2082.05</v>
       </c>
       <c r="I47" t="n">
         <v>1987.799991306485</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.46</v>
+        <v>-9.57</v>
       </c>
       <c r="L47" t="n">
-        <v>4.1</v>
+        <v>10.7</v>
       </c>
       <c r="M47" t="n">
         <v>1.86</v>
       </c>
       <c r="N47" t="n">
-        <v>3.44</v>
+        <v>5.91</v>
       </c>
       <c r="O47" t="n">
         <v>-0.52</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H48" t="n">
-        <v>2105.65</v>
+        <v>2013.1</v>
       </c>
       <c r="I48" t="n">
         <v>2021.683191099184</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K48" t="n">
-        <v>1.13</v>
+        <v>-3.31</v>
       </c>
       <c r="L48" t="n">
         <v>5.67</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>18.63</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45688</v>
+        <v>45689</v>
       </c>
       <c r="H49" t="n">
-        <v>1817.55</v>
+        <v>2056.65</v>
       </c>
       <c r="I49" t="n">
         <v>2036.010023090284</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K49" t="n">
-        <v>9.710000000000001</v>
+        <v>-2.16</v>
       </c>
       <c r="L49" t="n">
         <v>4.76</v>
@@ -3234,7 +3821,7 @@
         <v>3.31</v>
       </c>
       <c r="N49" t="n">
-        <v>3.65</v>
+        <v>13.16</v>
       </c>
       <c r="O49" t="n">
         <v>-4.4</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>21.27</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45770</v>
+        <v>45771</v>
       </c>
       <c r="H50" t="n">
-        <v>1925.4</v>
+        <v>1849.6</v>
       </c>
       <c r="I50" t="n">
         <v>1914.40491478291</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K50" t="n">
-        <v>-6.38</v>
+        <v>-10.07</v>
       </c>
       <c r="L50" t="n">
         <v>19.48</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>19.08</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45838</v>
+        <v>45839</v>
       </c>
       <c r="H51" t="n">
-        <v>1635.6</v>
+        <v>1704.9</v>
       </c>
       <c r="I51" t="n">
         <v>1683.94288016891</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K51" t="n">
-        <v>11.57</v>
+        <v>7.82</v>
       </c>
       <c r="L51" t="n">
         <v>5.81</v>
@@ -3348,7 +3959,7 @@
         <v>3.01</v>
       </c>
       <c r="N51" t="n">
-        <v>3.51</v>
+        <v>4.24</v>
       </c>
       <c r="O51" t="n">
         <v>-3.94</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>10.31</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H52" t="n">
-        <v>1747.2</v>
+        <v>1738.7</v>
       </c>
       <c r="I52" t="n">
         <v>1739.275173627523</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K52" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="L52" t="n">
         <v>4.3</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>8.56</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45883</v>
+        <v>45887</v>
       </c>
       <c r="H53" t="n">
-        <v>1785.2</v>
+        <v>1915.7</v>
       </c>
       <c r="I53" t="n">
         <v>1850.078505332543</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.67</v>
+        <v>-10.18</v>
       </c>
       <c r="L53" t="n">
-        <v>5.77</v>
+        <v>11.55</v>
       </c>
       <c r="M53" t="n">
-        <v>0.3</v>
+        <v>3.63</v>
       </c>
       <c r="N53" t="n">
-        <v>3.23</v>
+        <v>7.31</v>
       </c>
       <c r="O53" t="n">
         <v>-0.49</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>11.31</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="H54" t="n">
-        <v>1917.6</v>
+        <v>1785.5</v>
       </c>
       <c r="I54" t="n">
         <v>1860.036716204578</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1</v>
+        <v>-6.8</v>
       </c>
       <c r="L54" t="n">
-        <v>4.14</v>
+        <v>7.29</v>
       </c>
       <c r="M54" t="n">
         <v>1.13</v>
       </c>
       <c r="N54" t="n">
-        <v>3.05</v>
+        <v>6.89</v>
       </c>
       <c r="O54" t="n">
         <v>7.31</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>17.75</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="H55" t="n">
-        <v>1826.8</v>
+        <v>1854.6</v>
       </c>
       <c r="I55" t="n">
         <v>1840.656870262429</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.31</v>
+        <v>-3.87</v>
       </c>
       <c r="L55" t="n">
         <v>13.21</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>7.07</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="H56" t="n">
-        <v>1731.6</v>
+        <v>1708</v>
       </c>
       <c r="I56" t="n">
         <v>1723.5018747768</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.63</v>
+        <v>-7.9</v>
       </c>
       <c r="L56" t="n">
-        <v>6.81</v>
+        <v>8.23</v>
       </c>
       <c r="M56" t="n">
         <v>0.37</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.88</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H57" t="n">
-        <v>1816.1</v>
+        <v>1848.9</v>
       </c>
       <c r="I57" t="n">
         <v>1842.637220735068</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>-6.33</v>
+        <v>-8.25</v>
       </c>
       <c r="L57" t="n">
-        <v>7.11</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="M57" t="n">
         <v>0.64</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>10.2</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="H58" t="n">
-        <v>1698.1</v>
+        <v>1667.5</v>
       </c>
       <c r="I58" t="n">
         <v>1674.266622712801</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.16</v>
+        <v>-9.81</v>
       </c>
       <c r="L58" t="n">
-        <v>8.59</v>
+        <v>10.68</v>
       </c>
       <c r="M58" t="n">
         <v>0.85</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>10.13</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46054</v>
+        <v>46055</v>
       </c>
       <c r="H59" t="n">
-        <v>1793.4</v>
+        <v>1838.2</v>
       </c>
       <c r="I59" t="n">
         <v>1836.42494885013</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.55</v>
+        <v>-10.24</v>
       </c>
       <c r="L59" t="n">
-        <v>9.74</v>
+        <v>10.88</v>
       </c>
       <c r="M59" t="n">
         <v>0.85</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>12.41</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="H60" t="n">
-        <v>1833.2</v>
+        <v>1804.1</v>
       </c>
       <c r="I60" t="n">
         <v>1825.743074708951</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.27</v>
+        <v>-1.86</v>
       </c>
       <c r="L60" t="n">
         <v>3.93</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>12.37</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H61" t="n">
-        <v>1730</v>
+        <v>1804.9</v>
       </c>
       <c r="I61" t="n">
         <v>1748.36077619591</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K61" t="n">
-        <v>4.11</v>
+        <v>-0.04</v>
       </c>
       <c r="L61" t="n">
         <v>2.67</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>15.15</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="H62" t="n">
-        <v>1692.8</v>
+        <v>1661.1</v>
       </c>
       <c r="I62" t="n">
         <v>1686.030244703053</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.21</v>
+        <v>-7.97</v>
       </c>
       <c r="L62" t="n">
-        <v>6.37</v>
+        <v>8.69</v>
       </c>
       <c r="M62" t="n">
         <v>1.18</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>12.36</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="H63" t="n">
-        <v>1662</v>
+        <v>1716.1</v>
       </c>
       <c r="I63" t="n">
         <v>1714.229693812961</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.05</v>
+        <v>-3.31</v>
       </c>
       <c r="L63" t="n">
-        <v>3.41</v>
+        <v>3.68</v>
       </c>
       <c r="M63" t="n">
         <v>2.16</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.77</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="H64" t="n">
-        <v>1665</v>
+        <v>1571</v>
       </c>
       <c r="I64" t="n">
         <v>1613.903301040346</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.98</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>6.69</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M64" t="n">
         <v>0.71</v>
       </c>
       <c r="N64" t="n">
-        <v>3.15</v>
+        <v>5.65</v>
       </c>
       <c r="O64" t="n">
         <v>3.26</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,25 +4904,25 @@
         <v>13.62</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H65" t="n">
-        <v>1565</v>
+        <v>1575.4</v>
       </c>
       <c r="I65" t="n">
         <v>1572.531733843365</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K65" t="n">
-        <v>0.38</v>
+        <v>-0.28</v>
       </c>
       <c r="L65" t="n">
         <v>6.4</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="N65" t="n">
         <v>3.92</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4206,6 +4997,14 @@
       <c r="Q66" t="n">
         <v>21</v>
       </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9164,7 +9963,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65.09999999999999</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="6">
@@ -9174,7 +9973,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.5</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7">
@@ -9184,7 +9983,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8">
@@ -9194,7 +9993,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -9204,7 +10003,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -9214,7 +10013,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>110.7</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="11">
@@ -9224,7 +10023,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -9234,7 +10033,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -9244,7 +10043,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.7</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="14">
@@ -9254,7 +10053,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.03</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="15">
@@ -9264,7 +10063,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.85</v>
+        <v>6.91</v>
       </c>
     </row>
     <row r="16">
@@ -9274,7 +10073,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.2</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="17">
@@ -9284,7 +10083,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>140.85</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="18">
@@ -9294,7 +10093,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>45.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -9304,7 +10103,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.51</v>
+        <v>7.41</v>
       </c>
     </row>
     <row r="20">
@@ -9314,7 +10113,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.28</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="21">
@@ -9334,7 +10133,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -9344,7 +10143,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -9354,7 +10153,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="25">
@@ -9374,7 +10173,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.1</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="27">
@@ -9384,7 +10183,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.960000000000001</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="28">
@@ -9394,7 +10193,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
